--- a/artfynd/A 18465-2024 artfynd.xlsx
+++ b/artfynd/A 18465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118318075</v>
+        <v>118318073</v>
       </c>
       <c r="B2" t="n">
-        <v>100107</v>
+        <v>100017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416489</v>
+        <v>416518</v>
       </c>
       <c r="R2" t="n">
-        <v>6615014</v>
+        <v>6615067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118318091</v>
+        <v>118318071</v>
       </c>
       <c r="B3" t="n">
         <v>100107</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416527</v>
+        <v>416541</v>
       </c>
       <c r="R3" t="n">
-        <v>6615102</v>
+        <v>6615081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118318087</v>
+        <v>118318092</v>
       </c>
       <c r="B4" t="n">
-        <v>100017</v>
+        <v>90522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416501</v>
+        <v>416526</v>
       </c>
       <c r="R4" t="n">
-        <v>6615115</v>
+        <v>6615089</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118318073</v>
+        <v>118318081</v>
       </c>
       <c r="B5" t="n">
-        <v>100017</v>
+        <v>90518</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416518</v>
+        <v>416468</v>
       </c>
       <c r="R5" t="n">
-        <v>6615067</v>
+        <v>6615089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1082,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1083,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118318081</v>
+        <v>118318082</v>
       </c>
       <c r="B6" t="n">
-        <v>90518</v>
+        <v>90469</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1125,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416468</v>
+        <v>416467</v>
       </c>
       <c r="R6" t="n">
-        <v>6615089</v>
+        <v>6615095</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118318092</v>
+        <v>118318077</v>
       </c>
       <c r="B7" t="n">
-        <v>90522</v>
+        <v>100107</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416526</v>
+        <v>416488</v>
       </c>
       <c r="R7" t="n">
-        <v>6615089</v>
+        <v>6615022</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,21 +1316,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1317,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118318077</v>
+        <v>118318091</v>
       </c>
       <c r="B8" t="n">
         <v>100107</v>
@@ -1357,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416488</v>
+        <v>416527</v>
       </c>
       <c r="R8" t="n">
-        <v>6615022</v>
+        <v>6615102</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118318082</v>
+        <v>118318084</v>
       </c>
       <c r="B9" t="n">
-        <v>90469</v>
+        <v>100017</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416467</v>
+        <v>416486</v>
       </c>
       <c r="R9" t="n">
-        <v>6615095</v>
+        <v>6615166</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,21 +1520,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118318078</v>
+        <v>118318087</v>
       </c>
       <c r="B10" t="n">
         <v>100017</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416488</v>
+        <v>416501</v>
       </c>
       <c r="R10" t="n">
-        <v>6615023</v>
+        <v>6615115</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118318084</v>
+        <v>118318076</v>
       </c>
       <c r="B11" t="n">
         <v>100017</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416486</v>
+        <v>416489</v>
       </c>
       <c r="R11" t="n">
-        <v>6615166</v>
+        <v>6615015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118318076</v>
+        <v>118318078</v>
       </c>
       <c r="B12" t="n">
         <v>100017</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416489</v>
+        <v>416488</v>
       </c>
       <c r="R12" t="n">
-        <v>6615015</v>
+        <v>6615023</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118318089</v>
+        <v>118318075</v>
       </c>
       <c r="B13" t="n">
-        <v>100017</v>
+        <v>100107</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416520</v>
+        <v>416489</v>
       </c>
       <c r="R13" t="n">
-        <v>6615100</v>
+        <v>6615014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118318071</v>
+        <v>118318089</v>
       </c>
       <c r="B14" t="n">
-        <v>100107</v>
+        <v>100017</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416541</v>
+        <v>416520</v>
       </c>
       <c r="R14" t="n">
-        <v>6615081</v>
+        <v>6615100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 18465-2024 artfynd.xlsx
+++ b/artfynd/A 18465-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118318073</v>
+        <v>118318089</v>
       </c>
       <c r="B2" t="n">
         <v>100017</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416518</v>
+        <v>416520</v>
       </c>
       <c r="R2" t="n">
-        <v>6615067</v>
+        <v>6615100</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118318071</v>
+        <v>118318078</v>
       </c>
       <c r="B3" t="n">
-        <v>100107</v>
+        <v>100017</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416541</v>
+        <v>416488</v>
       </c>
       <c r="R3" t="n">
-        <v>6615081</v>
+        <v>6615023</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118318092</v>
+        <v>118318082</v>
       </c>
       <c r="B4" t="n">
-        <v>90522</v>
+        <v>90469</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416526</v>
+        <v>416467</v>
       </c>
       <c r="R4" t="n">
-        <v>6615089</v>
+        <v>6615095</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118318081</v>
+        <v>118318071</v>
       </c>
       <c r="B5" t="n">
-        <v>90518</v>
+        <v>100107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416468</v>
+        <v>416541</v>
       </c>
       <c r="R5" t="n">
-        <v>6615089</v>
+        <v>6615081</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,21 +1082,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1113,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118318082</v>
+        <v>118318076</v>
       </c>
       <c r="B6" t="n">
-        <v>90469</v>
+        <v>100017</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416467</v>
+        <v>416489</v>
       </c>
       <c r="R6" t="n">
-        <v>6615095</v>
+        <v>6615015</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,21 +1184,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118318077</v>
+        <v>118318084</v>
       </c>
       <c r="B7" t="n">
-        <v>100107</v>
+        <v>100017</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416488</v>
+        <v>416486</v>
       </c>
       <c r="R7" t="n">
-        <v>6615022</v>
+        <v>6615166</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1434,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118318084</v>
+        <v>118318077</v>
       </c>
       <c r="B9" t="n">
-        <v>100017</v>
+        <v>100107</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416486</v>
+        <v>416488</v>
       </c>
       <c r="R9" t="n">
-        <v>6615166</v>
+        <v>6615022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118318087</v>
+        <v>118318075</v>
       </c>
       <c r="B10" t="n">
-        <v>100017</v>
+        <v>100107</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416501</v>
+        <v>416489</v>
       </c>
       <c r="R10" t="n">
-        <v>6615115</v>
+        <v>6615014</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118318076</v>
+        <v>118318087</v>
       </c>
       <c r="B11" t="n">
         <v>100017</v>
@@ -1678,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416489</v>
+        <v>416501</v>
       </c>
       <c r="R11" t="n">
-        <v>6615015</v>
+        <v>6615115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118318078</v>
+        <v>118318092</v>
       </c>
       <c r="B12" t="n">
-        <v>100017</v>
+        <v>90522</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416488</v>
+        <v>416526</v>
       </c>
       <c r="R12" t="n">
-        <v>6615023</v>
+        <v>6615089</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,6 +1796,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1842,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118318075</v>
+        <v>118318081</v>
       </c>
       <c r="B13" t="n">
-        <v>100107</v>
+        <v>90518</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1839,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416489</v>
+        <v>416468</v>
       </c>
       <c r="R13" t="n">
-        <v>6615014</v>
+        <v>6615089</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,6 +1913,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1944,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118318089</v>
+        <v>118318073</v>
       </c>
       <c r="B14" t="n">
         <v>100017</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416520</v>
+        <v>416518</v>
       </c>
       <c r="R14" t="n">
-        <v>6615100</v>
+        <v>6615067</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 18465-2024 artfynd.xlsx
+++ b/artfynd/A 18465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118318089</v>
+        <v>118318073</v>
       </c>
       <c r="B2" t="n">
-        <v>100017</v>
+        <v>100024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416520</v>
+        <v>416518</v>
       </c>
       <c r="R2" t="n">
-        <v>6615100</v>
+        <v>6615067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118318078</v>
+        <v>118318091</v>
       </c>
       <c r="B3" t="n">
-        <v>100017</v>
+        <v>100114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416488</v>
+        <v>416527</v>
       </c>
       <c r="R3" t="n">
-        <v>6615023</v>
+        <v>6615102</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>118318082</v>
       </c>
       <c r="B4" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>118318071</v>
       </c>
       <c r="B5" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118318076</v>
+        <v>118318078</v>
       </c>
       <c r="B6" t="n">
-        <v>100017</v>
+        <v>100024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416489</v>
+        <v>416488</v>
       </c>
       <c r="R6" t="n">
-        <v>6615015</v>
+        <v>6615023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118318084</v>
+        <v>118318081</v>
       </c>
       <c r="B7" t="n">
-        <v>100017</v>
+        <v>90525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416486</v>
+        <v>416468</v>
       </c>
       <c r="R7" t="n">
-        <v>6615166</v>
+        <v>6615089</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1286,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1302,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118318091</v>
+        <v>118318087</v>
       </c>
       <c r="B8" t="n">
-        <v>100107</v>
+        <v>100024</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416527</v>
+        <v>416501</v>
       </c>
       <c r="R8" t="n">
-        <v>6615102</v>
+        <v>6615115</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118318077</v>
+        <v>118318089</v>
       </c>
       <c r="B9" t="n">
-        <v>100107</v>
+        <v>100024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416488</v>
+        <v>416520</v>
       </c>
       <c r="R9" t="n">
-        <v>6615022</v>
+        <v>6615100</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118318075</v>
+        <v>118318077</v>
       </c>
       <c r="B10" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416489</v>
+        <v>416488</v>
       </c>
       <c r="R10" t="n">
-        <v>6615014</v>
+        <v>6615022</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118318087</v>
+        <v>118318092</v>
       </c>
       <c r="B11" t="n">
-        <v>100017</v>
+        <v>90529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1635,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416501</v>
+        <v>416526</v>
       </c>
       <c r="R11" t="n">
-        <v>6615115</v>
+        <v>6615089</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1709,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1710,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118318092</v>
+        <v>118318084</v>
       </c>
       <c r="B12" t="n">
-        <v>90522</v>
+        <v>100024</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416526</v>
+        <v>416486</v>
       </c>
       <c r="R12" t="n">
-        <v>6615089</v>
+        <v>6615166</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,21 +1826,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1827,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118318081</v>
+        <v>118318075</v>
       </c>
       <c r="B13" t="n">
-        <v>90518</v>
+        <v>100114</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1839,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416468</v>
+        <v>416489</v>
       </c>
       <c r="R13" t="n">
-        <v>6615089</v>
+        <v>6615014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,21 +1928,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118318073</v>
+        <v>118318076</v>
       </c>
       <c r="B14" t="n">
-        <v>100017</v>
+        <v>100024</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416518</v>
+        <v>416489</v>
       </c>
       <c r="R14" t="n">
-        <v>6615067</v>
+        <v>6615015</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 18465-2024 artfynd.xlsx
+++ b/artfynd/A 18465-2024 artfynd.xlsx
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118318089</v>
+        <v>118318077</v>
       </c>
       <c r="B9" t="n">
-        <v>100024</v>
+        <v>100114</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416520</v>
+        <v>416488</v>
       </c>
       <c r="R9" t="n">
-        <v>6615100</v>
+        <v>6615022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118318077</v>
+        <v>118318089</v>
       </c>
       <c r="B10" t="n">
-        <v>100114</v>
+        <v>100024</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416488</v>
+        <v>416520</v>
       </c>
       <c r="R10" t="n">
-        <v>6615022</v>
+        <v>6615100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
